--- a/data/trans_orig/P17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2007</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2007 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35397</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47790</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>160137</t>
+          <t>159623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209643</t>
+          <t>208406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>78090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117998</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248070</t>
+          <t>250197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>309258</t>
+          <t>313020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151597</t>
+          <t>152172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>197663</t>
+          <t>195877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>248328</t>
+          <t>250821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>307616</t>
+          <t>309258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>413996</t>
+          <t>414437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>489686</t>
+          <t>490817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56881</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90233</t>
+          <t>88321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76376</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112912</t>
+          <t>115172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142836</t>
+          <t>142549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192409</t>
+          <t>193203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>541845</t>
+          <t>544553</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>605203</t>
+          <t>604858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802614</t>
+          <t>802408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>874725</t>
+          <t>871096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1367535</t>
+          <t>1370113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1461477</t>
+          <t>1457419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11579</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>32225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437367</t>
+          <t>443377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512726</t>
+          <t>513287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217357</t>
+          <t>218140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272937</t>
+          <t>273028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671263</t>
+          <t>676146</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>766151</t>
+          <t>772920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151267</t>
+          <t>152728</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>202675</t>
+          <t>201332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>316984</t>
+          <t>316791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378061</t>
+          <t>383395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>482337</t>
+          <t>482031</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562093</t>
+          <t>564080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168519</t>
+          <t>162714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219958</t>
+          <t>220326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155809</t>
+          <t>159347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208516</t>
+          <t>209490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338866</t>
+          <t>343989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414098</t>
+          <t>416074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>783727</t>
+          <t>776784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862888</t>
+          <t>860191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>754933</t>
+          <t>752842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>829944</t>
+          <t>832297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1559363</t>
+          <t>1554224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1674895</t>
+          <t>1668535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23249</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25436</t>
+          <t>25865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125118</t>
+          <t>126417</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170325</t>
+          <t>169063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>61290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92396</t>
+          <t>93965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198137</t>
+          <t>196985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250908</t>
+          <t>249630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>75186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69648</t>
+          <t>70321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104549</t>
+          <t>103753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122291</t>
+          <t>122513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166503</t>
+          <t>168258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77184</t>
+          <t>77854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112749</t>
+          <t>113339</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>39960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>67446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126952</t>
+          <t>126618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171416</t>
+          <t>171207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211366</t>
+          <t>209509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258328</t>
+          <t>258173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221143</t>
+          <t>221580</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267548</t>
+          <t>265000</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>447377</t>
+          <t>446162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>508738</t>
+          <t>509841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49569</t>
+          <t>48302</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83393</t>
+          <t>83009</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61899</t>
+          <t>61396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90619</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135443</t>
+          <t>135092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>753882</t>
+          <t>753059</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>858773</t>
+          <t>859011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376180</t>
+          <t>380387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>452717</t>
+          <t>456228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1159164</t>
+          <t>1157819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1285271</t>
+          <t>1286787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>367503</t>
+          <t>372666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>446232</t>
+          <t>451588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>665119</t>
+          <t>663545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>756429</t>
+          <t>756134</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1056489</t>
+          <t>1061833</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1178340</t>
+          <t>1176269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>322044</t>
+          <t>319761</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395820</t>
+          <t>395821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>297060</t>
+          <t>296473</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>366111</t>
+          <t>364573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>643821</t>
+          <t>641301</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>738551</t>
+          <t>743801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1578044</t>
+          <t>1573694</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1692511</t>
+          <t>1691361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1817794</t>
+          <t>1816905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1934341</t>
+          <t>1929458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3427518</t>
+          <t>3429401</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3587028</t>
+          <t>3582992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2012</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>17819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98528</t>
+          <t>98895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142186</t>
+          <t>140619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82438</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157194</t>
+          <t>158887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208649</t>
+          <t>209922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107865</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151996</t>
+          <t>152469</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>239094</t>
+          <t>242143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>298745</t>
+          <t>300760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361794</t>
+          <t>361713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>437680</t>
+          <t>435723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44900</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74738</t>
+          <t>74532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>48110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81565</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99776</t>
+          <t>100231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146503</t>
+          <t>142731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>619525</t>
+          <t>623381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681702</t>
+          <t>684318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898316</t>
+          <t>894316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965773</t>
+          <t>965289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1539692</t>
+          <t>1541544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1629231</t>
+          <t>1629818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>37538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>51058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344542</t>
+          <t>344472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417087</t>
+          <t>418207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136618</t>
+          <t>138606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186034</t>
+          <t>187174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495481</t>
+          <t>496151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588376</t>
+          <t>584870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285920</t>
+          <t>283948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>353873</t>
+          <t>350307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>420184</t>
+          <t>423206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>498916</t>
+          <t>495230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>726386</t>
+          <t>725203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>827697</t>
+          <t>829924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186911</t>
+          <t>190296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244371</t>
+          <t>249186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189942</t>
+          <t>187698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247322</t>
+          <t>245731</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395867</t>
+          <t>393378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>476242</t>
+          <t>473366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>980613</t>
+          <t>983054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1072481</t>
+          <t>1072948</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>864730</t>
+          <t>862868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954408</t>
+          <t>951804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1873038</t>
+          <t>1874092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2002142</t>
+          <t>2009740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80051</t>
+          <t>81838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118880</t>
+          <t>119728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>61195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122155</t>
+          <t>125158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171016</t>
+          <t>171450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59237</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>96174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>97330</t>
+          <t>95706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134875</t>
+          <t>137803</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170019</t>
+          <t>166110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>222399</t>
+          <t>218268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52635</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85244</t>
+          <t>86245</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36976</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>66850</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>101105</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143367</t>
+          <t>142545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201468</t>
+          <t>202525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249090</t>
+          <t>248439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210877</t>
+          <t>212698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255698</t>
+          <t>257830</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426835</t>
+          <t>423861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490596</t>
+          <t>492794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68183</t>
+          <t>67629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45842</t>
+          <t>46672</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63203</t>
+          <t>62036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102406</t>
+          <t>104092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>552983</t>
+          <t>552698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>645060</t>
+          <t>640075</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244874</t>
+          <t>237940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>310224</t>
+          <t>306075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>817272</t>
+          <t>809760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>922861</t>
+          <t>925964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>478462</t>
+          <t>472923</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>568792</t>
+          <t>565900</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>788354</t>
+          <t>792487</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>894398</t>
+          <t>896270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1300317</t>
+          <t>1293505</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1437139</t>
+          <t>1426922</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>310388</t>
+          <t>308123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379056</t>
+          <t>379929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>292541</t>
+          <t>293366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>365013</t>
+          <t>361741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623689</t>
+          <t>629076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>725433</t>
+          <t>733171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1844152</t>
+          <t>1848434</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1967720</t>
+          <t>1967690</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2013010</t>
+          <t>2011460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2132279</t>
+          <t>2130866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3886947</t>
+          <t>3897478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4067238</t>
+          <t>4063917</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2016</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>23554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>74696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111899</t>
+          <t>111453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>56053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>91791</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142267</t>
+          <t>141338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190944</t>
+          <t>190725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58586</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90720</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113017</t>
+          <t>113976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158318</t>
+          <t>161978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181801</t>
+          <t>181253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239121</t>
+          <t>235470</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>44821</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86292</t>
+          <t>87045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519366</t>
+          <t>519812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>572465</t>
+          <t>568703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>714134</t>
+          <t>713405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>771613</t>
+          <t>771482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1250762</t>
+          <t>1249706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1322053</t>
+          <t>1324714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61447</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>334813</t>
+          <t>335720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>407146</t>
+          <t>406646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158803</t>
+          <t>158378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210160</t>
+          <t>208528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509668</t>
+          <t>512538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600465</t>
+          <t>605504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216034</t>
+          <t>214502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273253</t>
+          <t>274662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>256222</t>
+          <t>258513</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322048</t>
+          <t>320674</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>489254</t>
+          <t>486317</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>578726</t>
+          <t>578703</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137880</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185953</t>
+          <t>187640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162705</t>
+          <t>163072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215070</t>
+          <t>214962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>310529</t>
+          <t>311232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>380914</t>
+          <t>381805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1225133</t>
+          <t>1225999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1316694</t>
+          <t>1318311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1251901</t>
+          <t>1256216</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1341538</t>
+          <t>1337956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2512854</t>
+          <t>2509303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2637127</t>
+          <t>2633238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36912</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112556</t>
+          <t>110717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151031</t>
+          <t>151883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>60204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>92913</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183068</t>
+          <t>180199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234681</t>
+          <t>233988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52948</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86034</t>
+          <t>85017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124370</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>148806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>197671</t>
+          <t>196689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52323</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47653</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78471</t>
+          <t>77195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82738</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>119586</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272222</t>
+          <t>271795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318090</t>
+          <t>319792</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272110</t>
+          <t>271227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>319414</t>
+          <t>317869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555851</t>
+          <t>555876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623381</t>
+          <t>620794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60619</t>
+          <t>60287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52086</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66746</t>
+          <t>65422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104852</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>549933</t>
+          <t>548202</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640104</t>
+          <t>638172</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297322</t>
+          <t>297638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>369520</t>
+          <t>368010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>863790</t>
+          <t>870157</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>981668</t>
+          <t>987145</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345769</t>
+          <t>345371</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>424407</t>
+          <t>423936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>483540</t>
+          <t>487820</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>572588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>851370</t>
+          <t>858709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>968755</t>
+          <t>972992</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>202289</t>
+          <t>201382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>261134</t>
+          <t>259515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>254364</t>
+          <t>253670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>317122</t>
+          <t>317727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>473738</t>
+          <t>467528</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>563394</t>
+          <t>556757</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2059551</t>
+          <t>2056404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2169843</t>
+          <t>2169882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2279946</t>
+          <t>2286002</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2396878</t>
+          <t>2398566</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4368434</t>
+          <t>4368740</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4531610</t>
+          <t>4535331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a usted o como acompañante durante el último año en 2023</t>
+          <t>Población que ha acudido a un centro de salud o ambulatorio de la Seguridad Social/SAS por algo que le pasaba a sí mismo/a o como acompañante durante el último año en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89388</t>
+          <t>86093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55312</t>
+          <t>56015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81736</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117551</t>
+          <t>118012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159896</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>49344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,42 +9891,42 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>90222</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>76984</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>108221</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>8,57%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>90222</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>76209</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>107668</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,47 +9964,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16082</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10751</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23196</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16082</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>10300</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24631</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>44016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360880</t>
+          <t>361202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397429</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597894</t>
+          <t>597911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>632454</t>
+          <t>631720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966508</t>
+          <t>968902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019309</t>
+          <t>1020014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49240</t>
+          <t>50781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365921</t>
+          <t>382628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629991</t>
+          <t>630690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227713</t>
+          <t>232773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>365196</t>
+          <t>363864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>693040</t>
+          <t>694104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972533</t>
+          <t>961714</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109025</t>
+          <t>112882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>199231</t>
+          <t>201944</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187158</t>
+          <t>198237</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>318537</t>
+          <t>318300</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>350782</t>
+          <t>345128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>502597</t>
+          <t>493957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119839</t>
+          <t>119248</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>978179</t>
+          <t>934890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121001</t>
+          <t>121445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200087</t>
+          <t>200606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284512</t>
+          <t>284848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1256051</t>
+          <t>1199028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>818369</t>
+          <t>830064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1356354</t>
+          <t>1358925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1365870</t>
+          <t>1369188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1700932</t>
+          <t>1679905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2204678</t>
+          <t>2218644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2903071</t>
+          <t>2926211</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145812</t>
+          <t>148669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193072</t>
+          <t>194369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109753</t>
+          <t>112881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146525</t>
+          <t>149165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272686</t>
+          <t>270904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328368</t>
+          <t>327091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>63096</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101475</t>
+          <t>101242</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80728</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112746</t>
+          <t>113537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149735</t>
+          <t>153379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200843</t>
+          <t>201642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>61089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>44197</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67192</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83287</t>
+          <t>83035</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121430</t>
+          <t>119804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>308960</t>
+          <t>311259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363004</t>
+          <t>366067</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>348444</t>
+          <t>349209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>394170</t>
+          <t>393813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>673399</t>
+          <t>676627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>745347</t>
+          <t>744101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56831</t>
+          <t>53178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65838</t>
+          <t>65946</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>604232</t>
+          <t>591104</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>865206</t>
+          <t>863149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>411075</t>
+          <t>408998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561141</t>
+          <t>561115</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1138903</t>
+          <t>1126514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1408413</t>
+          <t>1399889</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221168</t>
+          <t>223150</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>326937</t>
+          <t>323554</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>336335</t>
+          <t>340744</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>466839</t>
+          <t>468420</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>608841</t>
+          <t>607068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>770408</t>
+          <t>769274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183191</t>
+          <t>183308</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1164322</t>
+          <t>1075597</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198671</t>
+          <t>197433</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275937</t>
+          <t>271535</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>417664</t>
+          <t>411964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1514759</t>
+          <t>1485018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1446500</t>
+          <t>1530545</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2080256</t>
+          <t>2078935</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2364935</t>
+          <t>2358283</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2688609</t>
+          <t>2692611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3891093</t>
+          <t>3858173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4605993</t>
+          <t>4617281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36156</t>
+          <t>35887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>48148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159623</t>
+          <t>161205</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208406</t>
+          <t>211064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78090</t>
+          <t>75850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114321</t>
+          <t>113643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250197</t>
+          <t>248414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>313020</t>
+          <t>310573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>148030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195877</t>
+          <t>195093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250821</t>
+          <t>248783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>309258</t>
+          <t>306519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>414437</t>
+          <t>413134</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>490817</t>
+          <t>490268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54932</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88321</t>
+          <t>89330</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77984</t>
+          <t>75515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115172</t>
+          <t>114024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142549</t>
+          <t>141339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>193203</t>
+          <t>191269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>544553</t>
+          <t>543555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>604858</t>
+          <t>605576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802408</t>
+          <t>806805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>871096</t>
+          <t>873348</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1370113</t>
+          <t>1364917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1457419</t>
+          <t>1462815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>37407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11633</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61462</t>
+          <t>63550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443377</t>
+          <t>441200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513287</t>
+          <t>518077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218140</t>
+          <t>214520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273028</t>
+          <t>273368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>676146</t>
+          <t>666395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772920</t>
+          <t>767156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>149447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201332</t>
+          <t>201277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>316791</t>
+          <t>317107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>383395</t>
+          <t>381193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>482031</t>
+          <t>477019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>564080</t>
+          <t>562755</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162714</t>
+          <t>168453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220326</t>
+          <t>222578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159347</t>
+          <t>158574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209490</t>
+          <t>212035</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343989</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>416074</t>
+          <t>417596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776784</t>
+          <t>781651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>860191</t>
+          <t>862614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752842</t>
+          <t>751722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>832297</t>
+          <t>831652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1554224</t>
+          <t>1549048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1668535</t>
+          <t>1662945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126417</t>
+          <t>125718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169063</t>
+          <t>168730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61290</t>
+          <t>59222</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93965</t>
+          <t>92889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196985</t>
+          <t>194903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249630</t>
+          <t>248094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75186</t>
+          <t>73055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70321</t>
+          <t>70265</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103753</t>
+          <t>106476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122513</t>
+          <t>123019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168258</t>
+          <t>169875</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77854</t>
+          <t>79148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113339</t>
+          <t>114516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67446</t>
+          <t>68037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>126618</t>
+          <t>126151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171207</t>
+          <t>171920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209509</t>
+          <t>211280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258173</t>
+          <t>258891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221580</t>
+          <t>222566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265000</t>
+          <t>268529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>446162</t>
+          <t>445821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509841</t>
+          <t>511668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48302</t>
+          <t>51021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83009</t>
+          <t>84086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>33896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89176</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135092</t>
+          <t>136733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>753059</t>
+          <t>754491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>859011</t>
+          <t>857717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380387</t>
+          <t>378859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>456228</t>
+          <t>456917</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1157819</t>
+          <t>1154167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1286787</t>
+          <t>1284010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>372666</t>
+          <t>369908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>451588</t>
+          <t>445717</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>663545</t>
+          <t>663542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>756134</t>
+          <t>758175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1061833</t>
+          <t>1060406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1176269</t>
+          <t>1177739</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>319761</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>395821</t>
+          <t>397528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296473</t>
+          <t>295676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>364573</t>
+          <t>369384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>641301</t>
+          <t>638099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>743801</t>
+          <t>741585</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1573694</t>
+          <t>1578259</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1691361</t>
+          <t>1698630</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1816905</t>
+          <t>1816964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1929458</t>
+          <t>1931644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3429401</t>
+          <t>3419936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3582992</t>
+          <t>3587905</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>38931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98895</t>
+          <t>100111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>140619</t>
+          <t>140304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50934</t>
+          <t>49373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83495</t>
+          <t>84024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158887</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>209922</t>
+          <t>212922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107632</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152469</t>
+          <t>148930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242143</t>
+          <t>239412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300760</t>
+          <t>298596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361713</t>
+          <t>358817</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>435723</t>
+          <t>432544</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44519</t>
+          <t>44413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74532</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48110</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81047</t>
+          <t>81223</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100231</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142731</t>
+          <t>147206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>623381</t>
+          <t>622100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684318</t>
+          <t>684628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894316</t>
+          <t>896069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965289</t>
+          <t>967279</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1541544</t>
+          <t>1539746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1629818</t>
+          <t>1628771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23824</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51058</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344472</t>
+          <t>342080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418207</t>
+          <t>414687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138606</t>
+          <t>138283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187174</t>
+          <t>186669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496151</t>
+          <t>495815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584870</t>
+          <t>581946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283948</t>
+          <t>285472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>350307</t>
+          <t>350401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>423206</t>
+          <t>419732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>495230</t>
+          <t>496030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>725203</t>
+          <t>724080</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>829924</t>
+          <t>830377</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190296</t>
+          <t>189672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>249186</t>
+          <t>247201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187698</t>
+          <t>186930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245731</t>
+          <t>246228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>393378</t>
+          <t>396798</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>473366</t>
+          <t>476560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>983054</t>
+          <t>984183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1072948</t>
+          <t>1076896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>862868</t>
+          <t>863483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951804</t>
+          <t>949912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874092</t>
+          <t>1883449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2009740</t>
+          <t>2007995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>83076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119728</t>
+          <t>120344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>33117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61195</t>
+          <t>60249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125158</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171450</t>
+          <t>171279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>61298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96174</t>
+          <t>95690</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>95706</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>137803</t>
+          <t>135491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>166110</t>
+          <t>167163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>218268</t>
+          <t>221171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86245</t>
+          <t>88749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66850</t>
+          <t>65817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100550</t>
+          <t>99254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142545</t>
+          <t>143305</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202525</t>
+          <t>200290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248439</t>
+          <t>247627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212698</t>
+          <t>212483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257830</t>
+          <t>257366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>423861</t>
+          <t>427896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492794</t>
+          <t>490793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35443</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67629</t>
+          <t>69170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46672</t>
+          <t>44229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>63931</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104092</t>
+          <t>103825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>552698</t>
+          <t>551446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640075</t>
+          <t>640661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>237940</t>
+          <t>239226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306075</t>
+          <t>306387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>809760</t>
+          <t>809430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925964</t>
+          <t>925118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>472923</t>
+          <t>483412</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>565900</t>
+          <t>565141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>792487</t>
+          <t>792001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>896270</t>
+          <t>898934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1293505</t>
+          <t>1295868</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1426922</t>
+          <t>1435652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>308123</t>
+          <t>311090</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>379929</t>
+          <t>383205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>293366</t>
+          <t>294942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>361741</t>
+          <t>367227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>629076</t>
+          <t>624310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>733171</t>
+          <t>723696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1848434</t>
+          <t>1844569</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1967690</t>
+          <t>1966226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2011460</t>
+          <t>2009696</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2130866</t>
+          <t>2136592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3897478</t>
+          <t>3901136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4063917</t>
+          <t>4068209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74696</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111453</t>
+          <t>110409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56053</t>
+          <t>57379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91791</t>
+          <t>91606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141338</t>
+          <t>141882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190725</t>
+          <t>190655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58388</t>
+          <t>58479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>90578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113976</t>
+          <t>111985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>157649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181253</t>
+          <t>184375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>235470</t>
+          <t>237058</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44821</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87045</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519812</t>
+          <t>519173</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>568703</t>
+          <t>570459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>713405</t>
+          <t>716157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>771482</t>
+          <t>772067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1249706</t>
+          <t>1250777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1324714</t>
+          <t>1322617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36900</t>
+          <t>37192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,82 +7348,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>20492</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13155</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31472</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>45561</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>32391</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>60324</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20492</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13098</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>31826</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>45561</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>33289</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>60755</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335720</t>
+          <t>335855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406646</t>
+          <t>408101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158378</t>
+          <t>160724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208528</t>
+          <t>212423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>512538</t>
+          <t>506487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>605504</t>
+          <t>602531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214502</t>
+          <t>215535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274662</t>
+          <t>278854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>258513</t>
+          <t>257919</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320674</t>
+          <t>322249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>486317</t>
+          <t>488650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>578703</t>
+          <t>579914</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>139111</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187640</t>
+          <t>186414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163072</t>
+          <t>160796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214962</t>
+          <t>215241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311232</t>
+          <t>314340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>381805</t>
+          <t>385113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1225999</t>
+          <t>1229785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1318311</t>
+          <t>1322039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1256216</t>
+          <t>1255820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1337956</t>
+          <t>1342603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2509303</t>
+          <t>2504702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2633238</t>
+          <t>2633362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22757</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>111145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151883</t>
+          <t>152563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60204</t>
+          <t>60517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92913</t>
+          <t>91951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180199</t>
+          <t>178988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233988</t>
+          <t>232393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>85959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126446</t>
+          <t>124002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>147009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>196689</t>
+          <t>196420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>51410</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77195</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>80409</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119586</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271795</t>
+          <t>271689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319792</t>
+          <t>319651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271227</t>
+          <t>273332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317869</t>
+          <t>319360</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555876</t>
+          <t>559113</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>620794</t>
+          <t>625876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34074</t>
+          <t>33251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60287</t>
+          <t>61831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51881</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65422</t>
+          <t>67272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>104122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>548202</t>
+          <t>549644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638172</t>
+          <t>636343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297638</t>
+          <t>299400</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>368010</t>
+          <t>368665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>870157</t>
+          <t>868796</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>987145</t>
+          <t>982806</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>345371</t>
+          <t>347162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>423936</t>
+          <t>423716</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>487820</t>
+          <t>488500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>572588</t>
+          <t>570865</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>858709</t>
+          <t>857418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>972992</t>
+          <t>972646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>201382</t>
+          <t>201298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259515</t>
+          <t>261524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>253670</t>
+          <t>252983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>317727</t>
+          <t>317662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>467528</t>
+          <t>474641</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>556757</t>
+          <t>562982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2056404</t>
+          <t>2058615</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2169882</t>
+          <t>2169631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2286002</t>
+          <t>2281684</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2398566</t>
+          <t>2394999</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4368740</t>
+          <t>4380862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4535331</t>
+          <t>4528444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,74%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9718,102 +9718,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70203</t>
+          <t>93303</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86093</t>
+          <t>114196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59458</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87201</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>166433</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>143679</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>191408</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>13,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67368</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56015</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80225</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>137571</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>118012</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>159367</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9831,22 +9831,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>54991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>56111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>45093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64267</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>90222</t>
+          <t>98207</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76984</t>
+          <t>81672</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>114684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33269</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>28802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>49921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>380528</t>
+          <t>412802</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361202</t>
+          <t>388787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>433514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>615015</t>
+          <t>670367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597911</t>
+          <t>652459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>631720</t>
+          <t>687991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>995544</t>
+          <t>1083169</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>968902</t>
+          <t>1055449</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020014</t>
+          <t>1111580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511447</t>
+          <t>574620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511447</t>
+          <t>574620</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511447</t>
+          <t>574620</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>751970</t>
+          <t>819952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>751970</t>
+          <t>819952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>751970</t>
+          <t>819952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1263417</t>
+          <t>1394572</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1263417</t>
+          <t>1394572</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1263417</t>
+          <t>1394572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43140</t>
+          <t>44795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>31367</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50781</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>545102</t>
+          <t>612234</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382628</t>
+          <t>563707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630690</t>
+          <t>671163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311510</t>
+          <t>365747</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232773</t>
+          <t>333123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>363864</t>
+          <t>404494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>856611</t>
+          <t>977981</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694104</t>
+          <t>915624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>961714</t>
+          <t>1039142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164201</t>
+          <t>188002</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112882</t>
+          <t>160170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201944</t>
+          <t>218833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>272092</t>
+          <t>314104</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>198237</t>
+          <t>280050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>318300</t>
+          <t>342766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>436293</t>
+          <t>502106</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>345128</t>
+          <t>460902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>493957</t>
+          <t>551134</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>359458</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119248</t>
+          <t>101071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>151573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>169095</t>
+          <t>184422</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121445</t>
+          <t>162732</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200606</t>
+          <t>211159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>528553</t>
+          <t>310906</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284848</t>
+          <t>279649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1199028</t>
+          <t>346071</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1193360</t>
+          <t>1272671</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830064</t>
+          <t>1218256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1358925</t>
+          <t>1323179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1476102</t>
+          <t>1296011</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1369188</t>
+          <t>1249494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1679905</t>
+          <t>1338403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2669462</t>
+          <t>2568681</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2218644</t>
+          <t>2499871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2926211</t>
+          <t>2638783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2284849</t>
+          <t>2225183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2284849</t>
+          <t>2225183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2284849</t>
+          <t>2225183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2233019</t>
+          <t>2165858</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2233019</t>
+          <t>2165858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2233019</t>
+          <t>2165858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4517868</t>
+          <t>4391040</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4517868</t>
+          <t>4391040</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4517868</t>
+          <t>4391040</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,102 +10969,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11826</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>13552</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10680</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>11440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>6231</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>19004</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169928</t>
+          <t>190120</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148669</t>
+          <t>165956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194369</t>
+          <t>215362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>128890</t>
+          <t>143269</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112881</t>
+          <t>125090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149165</t>
+          <t>164042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>298818</t>
+          <t>333390</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270904</t>
+          <t>302018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>327091</t>
+          <t>365384</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>95799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63096</t>
+          <t>76787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101242</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>95736</t>
+          <t>112271</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>95559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>133071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>174351</t>
+          <t>208069</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>153379</t>
+          <t>181404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>201642</t>
+          <t>239376</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61089</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44197</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>77229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>100786</t>
+          <t>111064</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83035</t>
+          <t>91651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119804</t>
+          <t>130961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>336913</t>
+          <t>368378</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>311259</t>
+          <t>339374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366067</t>
+          <t>396408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>372307</t>
+          <t>407100</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349209</t>
+          <t>383630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>393813</t>
+          <t>430911</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>709220</t>
+          <t>775478</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676627</t>
+          <t>736610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>744101</t>
+          <t>813482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>636549</t>
+          <t>709246</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>636549</t>
+          <t>709246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>636549</t>
+          <t>709246</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658066</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658066</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658066</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1294615</t>
+          <t>1441553</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1294615</t>
+          <t>1441553</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1294615</t>
+          <t>1441553</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>34215</t>
+          <t>40074</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19741</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>58259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>53300</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>38518</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65946</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>785233</t>
+          <t>895658</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591104</t>
+          <t>839714</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>863149</t>
+          <t>960895</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>507768</t>
+          <t>582145</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408998</t>
+          <t>538740</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561115</t>
+          <t>629406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1293000</t>
+          <t>1477803</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1126514</t>
+          <t>1404787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1399889</t>
+          <t>1558339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280851</t>
+          <t>325896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>223150</t>
+          <t>288399</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323554</t>
+          <t>367121</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>420015</t>
+          <t>482485</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>340744</t>
+          <t>447484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>468420</t>
+          <t>526624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>700866</t>
+          <t>808381</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>607068</t>
+          <t>753390</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>769274</t>
+          <t>865479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>421745</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>183308</t>
+          <t>163122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1075597</t>
+          <t>225541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>240864</t>
+          <t>266782</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>197433</t>
+          <t>239097</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>271535</t>
+          <t>296376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>662608</t>
+          <t>460353</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>411964</t>
+          <t>421274</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1485018</t>
+          <t>502170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1910802</t>
+          <t>2053851</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1530545</t>
+          <t>1982829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2078935</t>
+          <t>2118554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2463423</t>
+          <t>2373477</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2358283</t>
+          <t>2321267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2692611</t>
+          <t>2425251</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4374226</t>
+          <t>4427328</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3858173</t>
+          <t>4338364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4617281</t>
+          <t>4510892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3432845</t>
+          <t>3509049</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3432845</t>
+          <t>3509049</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3432845</t>
+          <t>3509049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643054</t>
+          <t>3718116</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643054</t>
+          <t>3718116</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643054</t>
+          <t>3718116</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7075900</t>
+          <t>7227165</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7075900</t>
+          <t>7227165</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7075900</t>
+          <t>7227165</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
